--- a/benchmark/generated_files/RIC-1_V_039.xlsx
+++ b/benchmark/generated_files/RIC-1_V_039.xlsx
@@ -446,35 +446,28 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Periodo: 01/01/2026 - 28/02/2026</t>
+          <t>IBAN: IT76 P076 0101 6000 0109 8765 432</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Saldo iniziale: 11.163,02 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Divisa: EUR</t>
+          <t>Periodo: 01/01/2026 - 28/02/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Banca: PostePay Evolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>IBAN: IT76 P076 0101 6000 0109 8765 432</t>
+          <t>Codice cliente: 574723</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Filiale: SEDE CENTRALE</t>
         </is>
       </c>
     </row>
@@ -514,18 +507,18 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
+          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>-93.38</v>
+        <v>-54.31</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -535,18 +528,18 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 68,96 EUR DEL 02.01.2026 A (ITA) MACELLERIA BONI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4765 FUNSIDE OVEST</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-68.95999999999999</v>
+        <v>-254.84</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -556,18 +549,18 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 11,43 EUR DEL 02.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>Pagam. POS - PAGAMENTO POS 7,22 EUR DEL 01.01.2026 A (ITA) UNIEURO S.P.A.</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-11.43</v>
+        <v>-7.22</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -584,11 +577,11 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218222380 ORD. RICARICA POSTEPAY SOFIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 136,38 EUR DEL 02.01.2026 A (ITA) CONAD CITY ROMA</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>129.64</v>
+        <v>-136.38</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -598,18 +591,18 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
+          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-11.53</v>
+        <v>-20.44</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -619,18 +612,18 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46029</v>
+        <v>46024</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46031</v>
+        <v>46024</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 15,45 EUR DEL 07.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4529 CONAD SUPERSTORE</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-15.45</v>
+        <v>-111.31</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -640,18 +633,18 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46031</v>
+        <v>46024</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46032</v>
+        <v>46024</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 96,37 EUR DEL 09.01.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Bonif. v/fav. - RIF:210401180 ORD. RICARICA POSTEPAY SOFIA</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>-96.37</v>
+        <v>133.62</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -661,18 +654,18 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46031</v>
+        <v>46025</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46032</v>
+        <v>46025</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216163147 ORD. RICARICA POSTEPAY SOFIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 40,74 EUR DEL 03.01.2026 A (ITA) CALZEDONIA GROUP</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>281.61</v>
+        <v>-40.74</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -682,18 +675,18 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46032</v>
+        <v>46027</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46032</v>
+        <v>46027</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 36,99 EUR DEL 10.01.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 524,29 EUR DEL 05.01.2026 A (ITA) CARTOLIBRERIA IL PAPIRO</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-36.99</v>
+        <v>-524.29</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -703,18 +696,18 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46034</v>
+        <v>46027</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46034</v>
+        <v>46028</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 84,26 EUR DEL 12.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Pagam. POS - PAGAMENTO POS 44,41 EUR DEL 05.01.2026 A (ITA) SCARPE&amp;SCARPE BOLOGNA</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-84.26000000000001</v>
+        <v>-44.41</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -724,18 +717,18 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46034</v>
+        <v>46027</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46034</v>
+        <v>46027</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 9,63 EUR DEL 12.01.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 681,28 EUR DEL 05.01.2026 A (ITA) BUCHHANDLUNG WALTHER KÖNIG EUR</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>-9.630000000000001</v>
+        <v>-681.28</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -745,18 +738,18 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46034</v>
+        <v>46027</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46034</v>
+        <v>46029</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 89,30 EUR DEL 05.01.2026 A (ITA) PRIMOR CORSICO</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-28.47</v>
+        <v>-89.3</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -766,18 +759,18 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46035</v>
+        <v>46029</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46035</v>
+        <v>46030</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 12,95 EUR DEL 13.01.2026 A (ITA) PANIFICIO TOSI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8856 PITAYA CAGLIARI</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-12.95</v>
+        <v>-15.93</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -787,18 +780,18 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46035</v>
+        <v>46029</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46036</v>
+        <v>46031</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>247.35</v>
+        <v>-14.23</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -808,18 +801,18 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46037</v>
+        <v>46029</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46037</v>
+        <v>46030</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:219128193 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-70.09</v>
+        <v>121.2</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -829,18 +822,18 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 62,16 EUR DEL 15.01.2026 A (ITA) CARTOLIBRERIA IL PAPIRO</t>
+          <t>Addebito SDD - ACI BOLLO AUTO TARGA PG725YZ</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-62.16</v>
+        <v>-54.28</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -850,18 +843,18 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46038</v>
+        <v>46033</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46038</v>
+        <v>46033</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 34,73 EUR DEL 16.01.2026 A (ITA) BAR CENTRALE</t>
+          <t>Pagam. POS - PAGAMENTO POS 45,69 EUR DEL 11.01.2026 A (ITA) STAZIONE Q8</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-34.73</v>
+        <v>-45.69</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -871,18 +864,18 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46038</v>
+        <v>46034</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46038</v>
+        <v>46034</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 41,53 EUR DEL 16.01.2026 A (ITA) CALZEDONIA GROUP</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6551 LIBRACCIO</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-41.53</v>
+        <v>-431.12</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -892,18 +885,18 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46040</v>
+        <v>46034</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46040</v>
+        <v>46036</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 62,57 EUR DEL 18.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4627 OVS S.P.A.</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-62.57</v>
+        <v>-86.7</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -913,18 +906,18 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46040</v>
+        <v>46035</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46041</v>
+        <v>46035</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 10,14 EUR DEL 13.01.2026 A (ITA) POKE HOUSE</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-475.72</v>
+        <v>-10.14</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -934,18 +927,18 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46041</v>
+        <v>46036</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46041</v>
+        <v>46036</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 70,30 EUR DEL 14.01.2026 A (ITA) BREWDOG BOLOGNA</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>144.75</v>
+        <v>-70.3</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -955,18 +948,18 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46042</v>
+        <v>46036</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46042</v>
+        <v>46037</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>Pagam. POS - PAGAMENTO POS 47,58 EUR DEL 14.01.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-13.74</v>
+        <v>-47.58</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -976,18 +969,18 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46043</v>
+        <v>46037</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46043</v>
+        <v>46038</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 9820 TRATTORIA LA PERGOLA</t>
+          <t>Addebito SDD - APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-41.75</v>
+        <v>-6.49</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -997,18 +990,18 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46043</v>
+        <v>46037</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 173,12 EUR DEL 21.01.2026 A (ITA) PANIFICIO TOSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 42,87 EUR DEL 15.01.2026 A (ITA) RISTORANTE DA GINO</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-173.12</v>
+        <v>-42.87</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -1018,18 +1011,18 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46044</v>
+        <v>46038</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 34,19 EUR DEL 22.01.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>Pagam. POS - PAGAMENTO POS 81,57 EUR DEL 16.01.2026 A (ITA) GULLIVER</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-34.19</v>
+        <v>-81.56999999999999</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -1039,18 +1032,18 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46046</v>
+        <v>46038</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 142,12 EUR DEL 23.01.2026 A (ITA) CALZEDONIA GROUP</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8242 CISALFA SPORT VOMERO</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-142.12</v>
+        <v>-22.75</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1060,18 +1053,18 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46045</v>
+        <v>46040</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46045</v>
+        <v>46040</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 50,75 EUR DEL 23.01.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Pagam. POS - PAGAMENTO POS 70,99 EUR DEL 18.01.2026 A (ITA) OAKBERRY AÇAÍ BOWLS</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-50.75</v>
+        <v>-70.98999999999999</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -1081,18 +1074,18 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46047</v>
+        <v>46040</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46049</v>
+        <v>46040</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - ACI BOLLO AUTO TARGA ME439TP</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9405 LA FELTRINELLI CENTRO COMM. IL LEONE</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-30.24</v>
+        <v>-772.16</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1102,18 +1095,18 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46047</v>
+        <v>46040</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46047</v>
+        <v>46040</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 26,36 EUR DEL 18.01.2026 A (ITA) OAKBERRY AÇAÍ BOWLS</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-75.14</v>
+        <v>-26.36</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1123,18 +1116,18 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46047</v>
+        <v>46042</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46047</v>
+        <v>46043</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 48,17 EUR DEL 20.01.2026 A (ITA) DECATHLON ASSAGO</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>228.83</v>
+        <v>-48.17</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -1144,18 +1137,18 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46047</v>
+        <v>46042</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46047</v>
+        <v>46042</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215308143 ORD. RICARICA POSTEPAY SOFIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 10,81 EUR DEL 20.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>291.9</v>
+        <v>-10.81</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1165,18 +1158,18 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46048</v>
+        <v>46042</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46048</v>
+        <v>46042</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:214598509 BEN. AFFITTO APPARTAMENTO SOFIA BOLOGNA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7182 ALICE CENTRO</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-434.29</v>
+        <v>-48.31</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -1186,18 +1179,18 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46048</v>
+        <v>46043</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46048</v>
+        <v>46043</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 39,35 EUR DEL 26.01.2026 A (ITA) TRENITALIA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:219774758 ORD. RICARICA POSTEPAY SOFIA</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-39.35</v>
+        <v>244.87</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1207,18 +1200,18 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46048</v>
+        <v>46043</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46048</v>
+        <v>46043</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 156,83 EUR DEL 26.01.2026 A (ITA) MACELLERIA BONI</t>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>-156.83</v>
+        <v>236.47</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1228,18 +1221,18 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - WIND TRE S.P.A. MOBILE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9668 UBIK</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>-20.9</v>
+        <v>-668.8099999999999</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1249,18 +1242,18 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 43,55 EUR DEL 22.01.2026 A (ITA) JULIUS MEINL</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>-56.29</v>
+        <v>-43.55</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1270,18 +1263,18 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46049</v>
+        <v>46045</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46051</v>
+        <v>46045</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>Pagam. POS - PAGAMENTO POS 147,38 EUR DEL 23.01.2026 A (ITA) SIGMA MILANO</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>-7.16</v>
+        <v>-147.38</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1291,18 +1284,18 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46050</v>
+        <v>46047</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46050</v>
+        <v>46047</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 47,20 EUR DEL 28.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>Pagam. POS - PAGAMENTO POS 38,41 EUR DEL 25.01.2026 A (ITA) DISTRIBUTORE ENI</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>-47.2</v>
+        <v>-38.41</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -1312,18 +1305,18 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46051</v>
+        <v>46047</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46051</v>
+        <v>46049</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 5761 TRATTORIA LA PERGOLA</t>
+          <t>Pagam. POS - PAGAMENTO POS 451,93 EUR DEL 25.01.2026 A (ITA) FUNSIDE COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>-32.78</v>
+        <v>-451.93</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1333,18 +1326,18 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46051</v>
+        <v>46048</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46052</v>
+        <v>46049</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 15,56 EUR DEL 29.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Pagam. POS - PAGAMENTO POS 69,51 EUR DEL 26.01.2026 A (ITA) THE COFFEE</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>-15.56</v>
+        <v>-69.51000000000001</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -1354,18 +1347,18 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46052</v>
+        <v>46049</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46052</v>
+        <v>46049</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 450,66 EUR DEL 27.01.2026 A (ITA) FUNSIDE</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>-319.3</v>
+        <v>-450.66</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -1375,18 +1368,18 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46053</v>
+        <v>46049</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46053</v>
+        <v>46050</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 20,64 EUR DEL 31.01.2026 A (ITA) MACELLERIA BONI</t>
+          <t>Pagam. POS - PAGAMENTO POS 78,07 EUR DEL 27.01.2026 A (ITA) PIZZERIA NAPOLI</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>-20.64</v>
+        <v>-78.06999999999999</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -1396,18 +1389,18 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46054</v>
+        <v>46050</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46056</v>
+        <v>46050</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 92,11 EUR DEL 28.01.2026 A (ITA) PANIFICIO TOSI</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>-38.91</v>
+        <v>-92.11</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -1417,18 +1410,18 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46055</v>
+        <v>46050</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46055</v>
+        <v>46050</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SARA ASSICURAZIONI RCA AUTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 109,67 EUR DEL 28.01.2026 A (ITA) CONAD CITY ROMA</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>-55.43</v>
+        <v>-109.67</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -1438,18 +1431,18 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46056</v>
+        <v>46051</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46056</v>
+        <v>46053</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:211589681 BEN. AFFITTO APPARTAMENTO SOFIA BOLOGNA</t>
+          <t>Pagam. POS - PAGAMENTO POS 53,53 EUR DEL 29.01.2026 A (ITA) DOPPIO MALTO ASSAGO</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>-97.98</v>
+        <v>-53.53</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -1459,18 +1452,18 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46056</v>
+        <v>46052</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 55,25 EUR DEL 03.02.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Pagam. POS - PAGAMENTO POS 60,65 EUR DEL 30.01.2026 A (ITA) DISTRIBUTORE ENI</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>-55.25</v>
+        <v>-60.65</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -1480,18 +1473,18 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46056</v>
+        <v>46052</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46058</v>
+        <v>46053</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 17,54 EUR DEL 03.02.2026 A (ITA) ITALO NTV S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:218163977 ORD. RICARICA POSTEPAY SOFIA</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>-17.54</v>
+        <v>288.6</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -1501,18 +1494,18 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46056</v>
+        <v>46053</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46057</v>
+        <v>46053</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9954 IPERCOOP</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>265.19</v>
+        <v>-147.67</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -1522,18 +1515,18 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46057</v>
+        <v>46053</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46058</v>
+        <v>46054</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:219581522 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-10.94</v>
+        <v>166.98</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -1543,18 +1536,18 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 72,22 EUR DEL 04.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>Pagam. POS - PAGAMENTO POS 59,09 EUR DEL 03.02.2026 A (ITA) O'TACOS PARMA</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>-72.22</v>
+        <v>-59.09</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -1564,18 +1557,18 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B59" s="2" t="n">
         <v>46058</v>
       </c>
-      <c r="B59" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 63,81 EUR DEL 05.02.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4300 FUNSIDE</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>-63.81</v>
+        <v>-82.03</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -1585,18 +1578,18 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46060</v>
+        <v>46057</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 62,48 EUR DEL 05.02.2026 A (ITA) STAZIONE Q8</t>
+          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>-62.48</v>
+        <v>-210.52</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -1606,18 +1599,18 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46060</v>
+        <v>46058</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6783 O'TACOS</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>-8.73</v>
+        <v>-70.33</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -1627,18 +1620,18 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 27,35 EUR DEL 06.02.2026 A (ITA) BAR CENTRALE</t>
+          <t>Pagam. POS - PAGAMENTO POS 122,88 EUR DEL 05.02.2026 A (ITA) TUODÌ</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>-27.35</v>
+        <v>-122.88</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -1648,18 +1641,18 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46060</v>
+        <v>46058</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213447616 ORD. RICARICA POSTEPAY SOFIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 42,67 EUR DEL 05.02.2026 A (ITA) IN'S MERCATO</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>167.58</v>
+        <v>-42.67</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -1669,18 +1662,18 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46061</v>
+        <v>46059</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46061</v>
+        <v>46059</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 9999 TRATTORIA LA PERGOLA</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-72.19</v>
+        <v>-8.76</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -1690,18 +1683,18 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46061</v>
+        <v>46059</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46063</v>
+        <v>46059</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 12,24 EUR DEL 08.02.2026 A (ITA) STAZIONE Q8</t>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-12.24</v>
+        <v>296.73</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -1711,18 +1704,18 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 58,86 EUR DEL 07.02.2026 A (ITA) ITALO NTV S.P.A.</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>159.62</v>
+        <v>-58.86</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
@@ -1732,18 +1725,18 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
+        <v>46061</v>
+      </c>
+      <c r="B67" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="B67" s="2" t="n">
-        <v>46063</v>
-      </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>-6.28</v>
+        <v>179.84</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -1760,11 +1753,11 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217751377 ORD. RICARICA POSTEPAY SOFIA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3975 IKEA CAFÉ</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>261.79</v>
+        <v>-29.32</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -1781,11 +1774,11 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 688,91 EUR DEL 10.02.2026 A (ITA) LIBRERIA FELTRINELLI</t>
+          <t>Disposizione - RIF:211093321 BEN. AFFITTO APPARTAMENTO SOFIA BOLOGNA</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>-688.91</v>
+        <v>-387.68</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -1802,11 +1795,11 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1052 100 MONTADITOS</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>-11.26</v>
+        <v>-16.88</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
@@ -1816,18 +1809,18 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4237 CISALFA SPORT PADOVA</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>225.15</v>
+        <v>-25.92</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -1840,15 +1833,15 @@
         <v>46064</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46066</v>
+        <v>46064</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 23,72 EUR DEL 11.02.2026 A (ITA) ITALO NTV S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4992 OVS S.P.A.</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>-23.72</v>
+        <v>-44.61</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -1858,18 +1851,18 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46065</v>
+        <v>46067</v>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 40,88 EUR DEL 11.02.2026 A (ITA) BAR CENTRALE</t>
+          <t>Bonif. v/fav. - RIF:214522066 ORD. RICARICA POSTEPAY SOFIA</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-40.88</v>
+        <v>146.72</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -1879,18 +1872,18 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46065</v>
+        <v>46067</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46065</v>
+        <v>46067</v>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 4208 ESSELUNGA S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 72,94 EUR DEL 14.02.2026 A (ITA) PANIFICIO TOSI</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-136.17</v>
+        <v>-72.94</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -1900,18 +1893,18 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46067</v>
+        <v>46070</v>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 2295 OVS S.P.A.</t>
+          <t>Addebito SDD - APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>-84.59999999999999</v>
+        <v>-7.39</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -1921,18 +1914,18 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 171,38 EUR DEL 16.02.2026 A (ITA) LIDL ITALIA SRL</t>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>-171.38</v>
+        <v>229.88</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
@@ -1942,18 +1935,18 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 12,70 EUR DEL 16.02.2026 A (ITA) STAZIONE Q8</t>
+          <t>Pagam. POS - PAGAMENTO POS 153,83 EUR DEL 18.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>-12.7</v>
+        <v>-153.83</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -1963,18 +1956,18 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 15,30 EUR DEL 18.02.2026 A (ITA) BLUESPIRIT VIMODRONE</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>276.3</v>
+        <v>-15.3</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -1984,18 +1977,18 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46071</v>
+        <v>46075</v>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>Addebito SDD - ACI BOLLO AUTO TARGA JP685MH</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>-8.880000000000001</v>
+        <v>-21.74</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -2005,18 +1998,18 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>Pagam. POS - PAGAMENTO POS 130,42 EUR DEL 20.02.2026 A (ITA) ZARA ITALIA SRL</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>-5.97</v>
+        <v>-130.42</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
@@ -2026,18 +2019,18 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46074</v>
+        <v>46073</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 41,24 EUR DEL 19.02.2026 A (ITA) DISTRIBUTORE ENI</t>
+          <t>Bonif. v/fav. - RIF:214678115 ORD. RICARICA POSTEPAY SOFIA</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-41.24</v>
+        <v>115.1</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -2047,18 +2040,18 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46072</v>
+        <v>46074</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46072</v>
+        <v>46075</v>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 124,78 EUR DEL 19.02.2026 A (ITA) LIDL ITALIA SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5701 LA FELTRINELLI VENEZIA</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-124.78</v>
+        <v>-358.39</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
@@ -2068,18 +2061,18 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46072</v>
+        <v>46074</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 12,73 EUR DEL 19.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2497 PANS &amp; COMPANY PRATI</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-12.73</v>
+        <v>-60.43</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -2089,18 +2082,18 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46072</v>
+        <v>46075</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46072</v>
+        <v>46075</v>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 58,99 EUR DEL 19.02.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Pagam. POS - PAGAMENTO POS 66,92 EUR DEL 22.02.2026 A (ITA) UDON PADOVA</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>-58.99</v>
+        <v>-66.92</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -2117,11 +2110,11 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 48,57 EUR DEL 22.02.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-215715333</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-48.57</v>
+        <v>-10.11</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -2138,11 +2131,11 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 172,00 EUR DEL 22.02.2026 A (ITA) PANIFICIO TOSI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7179 SPORTLER</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-172</v>
+        <v>-100</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -2152,18 +2145,18 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46075</v>
+        <v>46076</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
+          <t>Bonif. v/fav. - RIF:214677995 ORD. RICARICA POSTEPAY SOFIA</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-38.28</v>
+        <v>150.92</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -2173,18 +2166,18 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Pagam. POS - PAGAMENTO POS 76,13 EUR DEL 25.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>-32.29</v>
+        <v>-76.13</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -2194,18 +2187,18 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 1863 ESSELUNGA S.P.A.</t>
+          <t>Addebito SDD - ACI BOLLO AUTO TARGA SK877KM</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-148.8</v>
+        <v>-17.38</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -2215,18 +2208,18 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 27,91 EUR DEL 26.02.2026 A (ITA) L'ISOLA DEI TESORI</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-64.38</v>
+        <v>-27.91</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -2236,18 +2229,18 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4751 IKEA BISTRO TIBURTINA</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-50.09</v>
+        <v>-18.65</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -2257,18 +2250,18 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46078</v>
+        <v>46082</v>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211086937 ORD. RICARICA POSTEPAY SOFIA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6223 TRATTORIA LA PERGOLA</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>98.43000000000001</v>
+        <v>-70.76000000000001</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -2285,11 +2278,11 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>Bonif. v/fav. - RIF:218863771 ORD. RICARICA POSTEPAY SOFIA</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-11.36</v>
+        <v>100.84</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
@@ -2300,7 +2293,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Saldo finale: 15.717,58 EUR</t>
+          <t>Saldo finale: 2.380,44 EUR</t>
         </is>
       </c>
     </row>
